--- a/graph_results.xlsx
+++ b/graph_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dariofenoglio/Desktop/Federated-C2BM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF66E43D-E9F0-784B-86E9-8F9D98AEAF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A93743-F349-5541-A571-53FF0C294628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45180" yWindow="10480" windowWidth="29000" windowHeight="18960" activeTab="6" xr2:uid="{8C3DF6BF-8DDD-F446-8EAC-CCE1EEDA313F}"/>
+    <workbookView xWindow="3600" yWindow="1580" windowWidth="28800" windowHeight="21100" activeTab="6" xr2:uid="{8C3DF6BF-8DDD-F446-8EAC-CCE1EEDA313F}"/>
   </bookViews>
   <sheets>
     <sheet name="Asia" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="Insurance" sheetId="6" r:id="rId4"/>
     <sheet name="Hailfinder" sheetId="7" r:id="rId5"/>
     <sheet name="SIIM" sheetId="8" r:id="rId6"/>
-    <sheet name="baseline_comparison" sheetId="9" r:id="rId7"/>
+    <sheet name="baseline_comparison_0303" sheetId="9" r:id="rId7"/>
+    <sheet name="baseline_comparison_0606" sheetId="10" r:id="rId8"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="26">
   <si>
     <t>mean</t>
   </si>
@@ -118,12 +119,15 @@
   <si>
     <t>BN fusion</t>
   </si>
+  <si>
+    <t>Graph alteration prob: 0.6</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -173,6 +177,20 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -182,7 +200,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="45">
+  <borders count="48">
     <border>
       <left/>
       <right/>
@@ -740,11 +758,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -817,6 +876,69 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -849,42 +971,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -923,6 +1009,54 @@
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1377,130 +1511,130 @@
       <c r="T12" s="6"/>
     </row>
     <row r="13" spans="4:24" x14ac:dyDescent="0.2">
-      <c r="G13" s="59" t="s">
+      <c r="G13" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="60"/>
-      <c r="K13" s="60"/>
-      <c r="L13" s="60"/>
-      <c r="M13" s="60"/>
-      <c r="N13" s="60"/>
-      <c r="O13" s="60"/>
-      <c r="P13" s="60"/>
-      <c r="Q13" s="60"/>
-      <c r="R13" s="60"/>
-      <c r="S13" s="60"/>
-      <c r="T13" s="60"/>
-      <c r="U13" s="60"/>
-      <c r="V13" s="60"/>
-      <c r="W13" s="60"/>
-      <c r="X13" s="61"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="63"/>
+      <c r="L13" s="63"/>
+      <c r="M13" s="63"/>
+      <c r="N13" s="63"/>
+      <c r="O13" s="63"/>
+      <c r="P13" s="63"/>
+      <c r="Q13" s="63"/>
+      <c r="R13" s="63"/>
+      <c r="S13" s="63"/>
+      <c r="T13" s="63"/>
+      <c r="U13" s="63"/>
+      <c r="V13" s="63"/>
+      <c r="W13" s="63"/>
+      <c r="X13" s="64"/>
     </row>
     <row r="14" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G14" s="62"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="63"/>
-      <c r="K14" s="63"/>
-      <c r="L14" s="63"/>
-      <c r="M14" s="63"/>
-      <c r="N14" s="63"/>
-      <c r="O14" s="63"/>
-      <c r="P14" s="63"/>
-      <c r="Q14" s="63"/>
-      <c r="R14" s="63"/>
-      <c r="S14" s="63"/>
-      <c r="T14" s="63"/>
-      <c r="U14" s="63"/>
-      <c r="V14" s="63"/>
-      <c r="W14" s="63"/>
-      <c r="X14" s="64"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="66"/>
+      <c r="K14" s="66"/>
+      <c r="L14" s="66"/>
+      <c r="M14" s="66"/>
+      <c r="N14" s="66"/>
+      <c r="O14" s="66"/>
+      <c r="P14" s="66"/>
+      <c r="Q14" s="66"/>
+      <c r="R14" s="66"/>
+      <c r="S14" s="66"/>
+      <c r="T14" s="66"/>
+      <c r="U14" s="66"/>
+      <c r="V14" s="66"/>
+      <c r="W14" s="66"/>
+      <c r="X14" s="67"/>
     </row>
     <row r="15" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D15" s="65" t="s">
+      <c r="D15" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="E15" s="66"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="65">
+      <c r="E15" s="69"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="68">
         <v>0.1</v>
       </c>
-      <c r="H15" s="67"/>
-      <c r="I15" s="65">
+      <c r="H15" s="70"/>
+      <c r="I15" s="68">
         <v>0.2</v>
       </c>
-      <c r="J15" s="67"/>
-      <c r="K15" s="65">
+      <c r="J15" s="70"/>
+      <c r="K15" s="68">
         <v>0.3</v>
       </c>
-      <c r="L15" s="67"/>
-      <c r="M15" s="65">
+      <c r="L15" s="70"/>
+      <c r="M15" s="68">
         <v>0.4</v>
       </c>
-      <c r="N15" s="67"/>
-      <c r="O15" s="65">
+      <c r="N15" s="70"/>
+      <c r="O15" s="68">
         <v>0.5</v>
       </c>
-      <c r="P15" s="67"/>
-      <c r="Q15" s="65">
+      <c r="P15" s="70"/>
+      <c r="Q15" s="68">
         <v>0.6</v>
       </c>
-      <c r="R15" s="67"/>
-      <c r="S15" s="65">
+      <c r="R15" s="70"/>
+      <c r="S15" s="68">
         <v>0.7</v>
       </c>
-      <c r="T15" s="67"/>
-      <c r="U15" s="65">
+      <c r="T15" s="70"/>
+      <c r="U15" s="68">
         <v>0.8</v>
       </c>
-      <c r="V15" s="67"/>
-      <c r="W15" s="65">
+      <c r="V15" s="70"/>
+      <c r="W15" s="68">
         <v>0.9</v>
       </c>
-      <c r="X15" s="67"/>
+      <c r="X15" s="70"/>
     </row>
     <row r="16" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D16" s="8"/>
       <c r="E16" s="27"/>
       <c r="F16" s="9"/>
-      <c r="G16" s="48" t="s">
+      <c r="G16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="49"/>
-      <c r="I16" s="48" t="s">
+      <c r="H16" s="72"/>
+      <c r="I16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="J16" s="49"/>
-      <c r="K16" s="48" t="s">
+      <c r="J16" s="72"/>
+      <c r="K16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="L16" s="58"/>
-      <c r="M16" s="48" t="s">
+      <c r="L16" s="81"/>
+      <c r="M16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="N16" s="49"/>
-      <c r="O16" s="48" t="s">
+      <c r="N16" s="72"/>
+      <c r="O16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="P16" s="49"/>
-      <c r="Q16" s="48" t="s">
+      <c r="P16" s="72"/>
+      <c r="Q16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="R16" s="49"/>
-      <c r="S16" s="48" t="s">
+      <c r="R16" s="72"/>
+      <c r="S16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T16" s="49"/>
-      <c r="U16" s="50" t="s">
+      <c r="T16" s="72"/>
+      <c r="U16" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="V16" s="51"/>
-      <c r="W16" s="50" t="s">
+      <c r="V16" s="74"/>
+      <c r="W16" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="X16" s="51"/>
+      <c r="X16" s="74"/>
     </row>
     <row r="17" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D17" s="10"/>
@@ -1562,10 +1696,10 @@
       </c>
     </row>
     <row r="18" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D18" s="52" t="s">
+      <c r="D18" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="55">
+      <c r="E18" s="78">
         <v>0.3</v>
       </c>
       <c r="F18" s="29" t="s">
@@ -1627,8 +1761,8 @@
       </c>
     </row>
     <row r="19" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D19" s="53"/>
-      <c r="E19" s="56"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="79"/>
       <c r="F19" s="29" t="s">
         <v>13</v>
       </c>
@@ -1688,8 +1822,8 @@
       </c>
     </row>
     <row r="20" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D20" s="53"/>
-      <c r="E20" s="57"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="80"/>
       <c r="F20" s="29" t="s">
         <v>11</v>
       </c>
@@ -1749,8 +1883,8 @@
       </c>
     </row>
     <row r="21" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="53"/>
-      <c r="E21" s="55">
+      <c r="D21" s="76"/>
+      <c r="E21" s="78">
         <v>0.6</v>
       </c>
       <c r="F21" s="29" t="s">
@@ -1812,8 +1946,8 @@
       </c>
     </row>
     <row r="22" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D22" s="53"/>
-      <c r="E22" s="56"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="79"/>
       <c r="F22" s="29" t="s">
         <v>13</v>
       </c>
@@ -1873,8 +2007,8 @@
       </c>
     </row>
     <row r="23" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D23" s="53"/>
-      <c r="E23" s="57"/>
+      <c r="D23" s="76"/>
+      <c r="E23" s="80"/>
       <c r="F23" s="29" t="s">
         <v>11</v>
       </c>
@@ -1934,8 +2068,8 @@
       </c>
     </row>
     <row r="24" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="53"/>
-      <c r="E24" s="55">
+      <c r="D24" s="76"/>
+      <c r="E24" s="78">
         <v>0.9</v>
       </c>
       <c r="F24" s="29" t="s">
@@ -1997,8 +2131,8 @@
       </c>
     </row>
     <row r="25" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="53"/>
-      <c r="E25" s="56"/>
+      <c r="D25" s="76"/>
+      <c r="E25" s="79"/>
       <c r="F25" s="29" t="s">
         <v>13</v>
       </c>
@@ -2058,8 +2192,8 @@
       </c>
     </row>
     <row r="26" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="54"/>
-      <c r="E26" s="57"/>
+      <c r="D26" s="77"/>
+      <c r="E26" s="80"/>
       <c r="F26" s="29" t="s">
         <v>11</v>
       </c>
@@ -2196,17 +2330,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="G13:X14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="U15:V15"/>
-    <mergeCell ref="W15:X15"/>
-    <mergeCell ref="S15:T15"/>
     <mergeCell ref="Q16:R16"/>
     <mergeCell ref="S16:T16"/>
     <mergeCell ref="U16:V16"/>
@@ -2220,6 +2343,17 @@
     <mergeCell ref="K16:L16"/>
     <mergeCell ref="M16:N16"/>
     <mergeCell ref="O16:P16"/>
+    <mergeCell ref="G13:X14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="U15:V15"/>
+    <mergeCell ref="W15:X15"/>
+    <mergeCell ref="S15:T15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2232,130 +2366,130 @@
   <sheetData>
     <row r="12" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="4:24" x14ac:dyDescent="0.2">
-      <c r="G13" s="59" t="s">
+      <c r="G13" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="60"/>
-      <c r="K13" s="60"/>
-      <c r="L13" s="60"/>
-      <c r="M13" s="60"/>
-      <c r="N13" s="60"/>
-      <c r="O13" s="60"/>
-      <c r="P13" s="60"/>
-      <c r="Q13" s="60"/>
-      <c r="R13" s="60"/>
-      <c r="S13" s="60"/>
-      <c r="T13" s="60"/>
-      <c r="U13" s="60"/>
-      <c r="V13" s="60"/>
-      <c r="W13" s="60"/>
-      <c r="X13" s="61"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="63"/>
+      <c r="L13" s="63"/>
+      <c r="M13" s="63"/>
+      <c r="N13" s="63"/>
+      <c r="O13" s="63"/>
+      <c r="P13" s="63"/>
+      <c r="Q13" s="63"/>
+      <c r="R13" s="63"/>
+      <c r="S13" s="63"/>
+      <c r="T13" s="63"/>
+      <c r="U13" s="63"/>
+      <c r="V13" s="63"/>
+      <c r="W13" s="63"/>
+      <c r="X13" s="64"/>
     </row>
     <row r="14" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G14" s="62"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="63"/>
-      <c r="K14" s="63"/>
-      <c r="L14" s="63"/>
-      <c r="M14" s="63"/>
-      <c r="N14" s="63"/>
-      <c r="O14" s="63"/>
-      <c r="P14" s="63"/>
-      <c r="Q14" s="63"/>
-      <c r="R14" s="63"/>
-      <c r="S14" s="63"/>
-      <c r="T14" s="63"/>
-      <c r="U14" s="63"/>
-      <c r="V14" s="63"/>
-      <c r="W14" s="63"/>
-      <c r="X14" s="64"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="66"/>
+      <c r="K14" s="66"/>
+      <c r="L14" s="66"/>
+      <c r="M14" s="66"/>
+      <c r="N14" s="66"/>
+      <c r="O14" s="66"/>
+      <c r="P14" s="66"/>
+      <c r="Q14" s="66"/>
+      <c r="R14" s="66"/>
+      <c r="S14" s="66"/>
+      <c r="T14" s="66"/>
+      <c r="U14" s="66"/>
+      <c r="V14" s="66"/>
+      <c r="W14" s="66"/>
+      <c r="X14" s="67"/>
     </row>
     <row r="15" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D15" s="65" t="s">
+      <c r="D15" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="E15" s="66"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="65">
+      <c r="E15" s="69"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="68">
         <v>0.1</v>
       </c>
-      <c r="H15" s="67"/>
-      <c r="I15" s="65">
+      <c r="H15" s="70"/>
+      <c r="I15" s="68">
         <v>0.2</v>
       </c>
-      <c r="J15" s="67"/>
-      <c r="K15" s="65">
+      <c r="J15" s="70"/>
+      <c r="K15" s="68">
         <v>0.3</v>
       </c>
-      <c r="L15" s="67"/>
-      <c r="M15" s="65">
+      <c r="L15" s="70"/>
+      <c r="M15" s="68">
         <v>0.4</v>
       </c>
-      <c r="N15" s="67"/>
-      <c r="O15" s="65">
+      <c r="N15" s="70"/>
+      <c r="O15" s="68">
         <v>0.5</v>
       </c>
-      <c r="P15" s="67"/>
-      <c r="Q15" s="65">
+      <c r="P15" s="70"/>
+      <c r="Q15" s="68">
         <v>0.6</v>
       </c>
-      <c r="R15" s="67"/>
-      <c r="S15" s="65">
+      <c r="R15" s="70"/>
+      <c r="S15" s="68">
         <v>0.7</v>
       </c>
-      <c r="T15" s="67"/>
-      <c r="U15" s="65">
+      <c r="T15" s="70"/>
+      <c r="U15" s="68">
         <v>0.8</v>
       </c>
-      <c r="V15" s="67"/>
-      <c r="W15" s="65">
+      <c r="V15" s="70"/>
+      <c r="W15" s="68">
         <v>0.9</v>
       </c>
-      <c r="X15" s="67"/>
+      <c r="X15" s="70"/>
     </row>
     <row r="16" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D16" s="8"/>
       <c r="E16" s="27"/>
       <c r="F16" s="9"/>
-      <c r="G16" s="48" t="s">
+      <c r="G16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="49"/>
-      <c r="I16" s="48" t="s">
+      <c r="H16" s="72"/>
+      <c r="I16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="J16" s="49"/>
-      <c r="K16" s="48" t="s">
+      <c r="J16" s="72"/>
+      <c r="K16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="L16" s="58"/>
-      <c r="M16" s="48" t="s">
+      <c r="L16" s="81"/>
+      <c r="M16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="N16" s="49"/>
-      <c r="O16" s="48" t="s">
+      <c r="N16" s="72"/>
+      <c r="O16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="P16" s="49"/>
-      <c r="Q16" s="48" t="s">
+      <c r="P16" s="72"/>
+      <c r="Q16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="R16" s="49"/>
-      <c r="S16" s="48" t="s">
+      <c r="R16" s="72"/>
+      <c r="S16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T16" s="49"/>
-      <c r="U16" s="50" t="s">
+      <c r="T16" s="72"/>
+      <c r="U16" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="V16" s="51"/>
-      <c r="W16" s="50" t="s">
+      <c r="V16" s="74"/>
+      <c r="W16" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="X16" s="51"/>
+      <c r="X16" s="74"/>
     </row>
     <row r="17" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D17" s="10"/>
@@ -2417,10 +2551,10 @@
       </c>
     </row>
     <row r="18" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D18" s="52" t="s">
+      <c r="D18" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="55">
+      <c r="E18" s="78">
         <v>0.3</v>
       </c>
       <c r="F18" s="29" t="s">
@@ -2482,8 +2616,8 @@
       </c>
     </row>
     <row r="19" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D19" s="53"/>
-      <c r="E19" s="56"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="79"/>
       <c r="F19" s="29" t="s">
         <v>13</v>
       </c>
@@ -2543,8 +2677,8 @@
       </c>
     </row>
     <row r="20" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D20" s="53"/>
-      <c r="E20" s="57"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="80"/>
       <c r="F20" s="29" t="s">
         <v>11</v>
       </c>
@@ -2604,8 +2738,8 @@
       </c>
     </row>
     <row r="21" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="53"/>
-      <c r="E21" s="55">
+      <c r="D21" s="76"/>
+      <c r="E21" s="78">
         <v>0.6</v>
       </c>
       <c r="F21" s="29" t="s">
@@ -2667,8 +2801,8 @@
       </c>
     </row>
     <row r="22" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D22" s="53"/>
-      <c r="E22" s="56"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="79"/>
       <c r="F22" s="29" t="s">
         <v>13</v>
       </c>
@@ -2728,8 +2862,8 @@
       </c>
     </row>
     <row r="23" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D23" s="53"/>
-      <c r="E23" s="57"/>
+      <c r="D23" s="76"/>
+      <c r="E23" s="80"/>
       <c r="F23" s="29" t="s">
         <v>11</v>
       </c>
@@ -2789,8 +2923,8 @@
       </c>
     </row>
     <row r="24" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="53"/>
-      <c r="E24" s="55">
+      <c r="D24" s="76"/>
+      <c r="E24" s="78">
         <v>0.9</v>
       </c>
       <c r="F24" s="29" t="s">
@@ -2852,8 +2986,8 @@
       </c>
     </row>
     <row r="25" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="53"/>
-      <c r="E25" s="56"/>
+      <c r="D25" s="76"/>
+      <c r="E25" s="79"/>
       <c r="F25" s="29" t="s">
         <v>13</v>
       </c>
@@ -2913,8 +3047,8 @@
       </c>
     </row>
     <row r="26" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="54"/>
-      <c r="E26" s="57"/>
+      <c r="D26" s="77"/>
+      <c r="E26" s="80"/>
       <c r="F26" s="29" t="s">
         <v>11</v>
       </c>
@@ -2975,6 +3109,16 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="G13:X14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="S15:T15"/>
+    <mergeCell ref="U15:V15"/>
     <mergeCell ref="D18:D26"/>
     <mergeCell ref="E18:E20"/>
     <mergeCell ref="E21:E23"/>
@@ -2989,16 +3133,6 @@
     <mergeCell ref="S16:T16"/>
     <mergeCell ref="U16:V16"/>
     <mergeCell ref="W16:X16"/>
-    <mergeCell ref="G13:X14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="S15:T15"/>
-    <mergeCell ref="U15:V15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3011,130 +3145,130 @@
   <sheetData>
     <row r="12" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="4:24" x14ac:dyDescent="0.2">
-      <c r="G13" s="59" t="s">
+      <c r="G13" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="60"/>
-      <c r="K13" s="60"/>
-      <c r="L13" s="60"/>
-      <c r="M13" s="60"/>
-      <c r="N13" s="60"/>
-      <c r="O13" s="60"/>
-      <c r="P13" s="60"/>
-      <c r="Q13" s="60"/>
-      <c r="R13" s="60"/>
-      <c r="S13" s="60"/>
-      <c r="T13" s="60"/>
-      <c r="U13" s="60"/>
-      <c r="V13" s="60"/>
-      <c r="W13" s="60"/>
-      <c r="X13" s="61"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="63"/>
+      <c r="L13" s="63"/>
+      <c r="M13" s="63"/>
+      <c r="N13" s="63"/>
+      <c r="O13" s="63"/>
+      <c r="P13" s="63"/>
+      <c r="Q13" s="63"/>
+      <c r="R13" s="63"/>
+      <c r="S13" s="63"/>
+      <c r="T13" s="63"/>
+      <c r="U13" s="63"/>
+      <c r="V13" s="63"/>
+      <c r="W13" s="63"/>
+      <c r="X13" s="64"/>
     </row>
     <row r="14" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G14" s="62"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="63"/>
-      <c r="K14" s="63"/>
-      <c r="L14" s="63"/>
-      <c r="M14" s="63"/>
-      <c r="N14" s="63"/>
-      <c r="O14" s="63"/>
-      <c r="P14" s="63"/>
-      <c r="Q14" s="63"/>
-      <c r="R14" s="63"/>
-      <c r="S14" s="63"/>
-      <c r="T14" s="63"/>
-      <c r="U14" s="63"/>
-      <c r="V14" s="63"/>
-      <c r="W14" s="63"/>
-      <c r="X14" s="64"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="66"/>
+      <c r="K14" s="66"/>
+      <c r="L14" s="66"/>
+      <c r="M14" s="66"/>
+      <c r="N14" s="66"/>
+      <c r="O14" s="66"/>
+      <c r="P14" s="66"/>
+      <c r="Q14" s="66"/>
+      <c r="R14" s="66"/>
+      <c r="S14" s="66"/>
+      <c r="T14" s="66"/>
+      <c r="U14" s="66"/>
+      <c r="V14" s="66"/>
+      <c r="W14" s="66"/>
+      <c r="X14" s="67"/>
     </row>
     <row r="15" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D15" s="65" t="s">
+      <c r="D15" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="E15" s="66"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="65">
+      <c r="E15" s="69"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="68">
         <v>0.1</v>
       </c>
-      <c r="H15" s="67"/>
-      <c r="I15" s="65">
+      <c r="H15" s="70"/>
+      <c r="I15" s="68">
         <v>0.2</v>
       </c>
-      <c r="J15" s="67"/>
-      <c r="K15" s="65">
+      <c r="J15" s="70"/>
+      <c r="K15" s="68">
         <v>0.3</v>
       </c>
-      <c r="L15" s="67"/>
-      <c r="M15" s="65">
+      <c r="L15" s="70"/>
+      <c r="M15" s="68">
         <v>0.4</v>
       </c>
-      <c r="N15" s="67"/>
-      <c r="O15" s="65">
+      <c r="N15" s="70"/>
+      <c r="O15" s="68">
         <v>0.5</v>
       </c>
-      <c r="P15" s="67"/>
-      <c r="Q15" s="65">
+      <c r="P15" s="70"/>
+      <c r="Q15" s="68">
         <v>0.6</v>
       </c>
-      <c r="R15" s="67"/>
-      <c r="S15" s="65">
+      <c r="R15" s="70"/>
+      <c r="S15" s="68">
         <v>0.7</v>
       </c>
-      <c r="T15" s="67"/>
-      <c r="U15" s="65">
+      <c r="T15" s="70"/>
+      <c r="U15" s="68">
         <v>0.8</v>
       </c>
-      <c r="V15" s="67"/>
-      <c r="W15" s="65">
+      <c r="V15" s="70"/>
+      <c r="W15" s="68">
         <v>0.9</v>
       </c>
-      <c r="X15" s="67"/>
+      <c r="X15" s="70"/>
     </row>
     <row r="16" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D16" s="8"/>
       <c r="E16" s="27"/>
       <c r="F16" s="9"/>
-      <c r="G16" s="48" t="s">
+      <c r="G16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="49"/>
-      <c r="I16" s="48" t="s">
+      <c r="H16" s="72"/>
+      <c r="I16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="J16" s="49"/>
-      <c r="K16" s="48" t="s">
+      <c r="J16" s="72"/>
+      <c r="K16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="L16" s="58"/>
-      <c r="M16" s="48" t="s">
+      <c r="L16" s="81"/>
+      <c r="M16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="N16" s="49"/>
-      <c r="O16" s="48" t="s">
+      <c r="N16" s="72"/>
+      <c r="O16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="P16" s="49"/>
-      <c r="Q16" s="48" t="s">
+      <c r="P16" s="72"/>
+      <c r="Q16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="R16" s="49"/>
-      <c r="S16" s="48" t="s">
+      <c r="R16" s="72"/>
+      <c r="S16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T16" s="49"/>
-      <c r="U16" s="50" t="s">
+      <c r="T16" s="72"/>
+      <c r="U16" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="V16" s="51"/>
-      <c r="W16" s="50" t="s">
+      <c r="V16" s="74"/>
+      <c r="W16" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="X16" s="51"/>
+      <c r="X16" s="74"/>
     </row>
     <row r="17" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D17" s="10"/>
@@ -3196,10 +3330,10 @@
       </c>
     </row>
     <row r="18" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D18" s="52" t="s">
+      <c r="D18" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="55">
+      <c r="E18" s="78">
         <v>0.3</v>
       </c>
       <c r="F18" s="29" t="s">
@@ -3261,8 +3395,8 @@
       </c>
     </row>
     <row r="19" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D19" s="53"/>
-      <c r="E19" s="56"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="79"/>
       <c r="F19" s="29" t="s">
         <v>13</v>
       </c>
@@ -3322,8 +3456,8 @@
       </c>
     </row>
     <row r="20" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D20" s="53"/>
-      <c r="E20" s="57"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="80"/>
       <c r="F20" s="29" t="s">
         <v>11</v>
       </c>
@@ -3383,8 +3517,8 @@
       </c>
     </row>
     <row r="21" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="53"/>
-      <c r="E21" s="55">
+      <c r="D21" s="76"/>
+      <c r="E21" s="78">
         <v>0.6</v>
       </c>
       <c r="F21" s="29" t="s">
@@ -3446,8 +3580,8 @@
       </c>
     </row>
     <row r="22" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D22" s="53"/>
-      <c r="E22" s="56"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="79"/>
       <c r="F22" s="29" t="s">
         <v>13</v>
       </c>
@@ -3507,8 +3641,8 @@
       </c>
     </row>
     <row r="23" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D23" s="53"/>
-      <c r="E23" s="57"/>
+      <c r="D23" s="76"/>
+      <c r="E23" s="80"/>
       <c r="F23" s="29" t="s">
         <v>11</v>
       </c>
@@ -3568,8 +3702,8 @@
       </c>
     </row>
     <row r="24" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="53"/>
-      <c r="E24" s="55">
+      <c r="D24" s="76"/>
+      <c r="E24" s="78">
         <v>0.9</v>
       </c>
       <c r="F24" s="29" t="s">
@@ -3631,8 +3765,8 @@
       </c>
     </row>
     <row r="25" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="53"/>
-      <c r="E25" s="56"/>
+      <c r="D25" s="76"/>
+      <c r="E25" s="79"/>
       <c r="F25" s="29" t="s">
         <v>13</v>
       </c>
@@ -3692,8 +3826,8 @@
       </c>
     </row>
     <row r="26" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="54"/>
-      <c r="E26" s="57"/>
+      <c r="D26" s="77"/>
+      <c r="E26" s="80"/>
       <c r="F26" s="29" t="s">
         <v>11</v>
       </c>
@@ -3754,6 +3888,16 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="G13:X14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="S15:T15"/>
+    <mergeCell ref="U15:V15"/>
     <mergeCell ref="D18:D26"/>
     <mergeCell ref="E18:E20"/>
     <mergeCell ref="E21:E23"/>
@@ -3768,16 +3912,6 @@
     <mergeCell ref="S16:T16"/>
     <mergeCell ref="U16:V16"/>
     <mergeCell ref="W16:X16"/>
-    <mergeCell ref="G13:X14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="S15:T15"/>
-    <mergeCell ref="U15:V15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3790,130 +3924,130 @@
   <sheetData>
     <row r="12" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="4:24" x14ac:dyDescent="0.2">
-      <c r="G13" s="59" t="s">
+      <c r="G13" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="60"/>
-      <c r="K13" s="60"/>
-      <c r="L13" s="60"/>
-      <c r="M13" s="60"/>
-      <c r="N13" s="60"/>
-      <c r="O13" s="60"/>
-      <c r="P13" s="60"/>
-      <c r="Q13" s="60"/>
-      <c r="R13" s="60"/>
-      <c r="S13" s="60"/>
-      <c r="T13" s="60"/>
-      <c r="U13" s="60"/>
-      <c r="V13" s="60"/>
-      <c r="W13" s="60"/>
-      <c r="X13" s="61"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="63"/>
+      <c r="L13" s="63"/>
+      <c r="M13" s="63"/>
+      <c r="N13" s="63"/>
+      <c r="O13" s="63"/>
+      <c r="P13" s="63"/>
+      <c r="Q13" s="63"/>
+      <c r="R13" s="63"/>
+      <c r="S13" s="63"/>
+      <c r="T13" s="63"/>
+      <c r="U13" s="63"/>
+      <c r="V13" s="63"/>
+      <c r="W13" s="63"/>
+      <c r="X13" s="64"/>
     </row>
     <row r="14" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G14" s="62"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="63"/>
-      <c r="K14" s="63"/>
-      <c r="L14" s="63"/>
-      <c r="M14" s="63"/>
-      <c r="N14" s="63"/>
-      <c r="O14" s="63"/>
-      <c r="P14" s="63"/>
-      <c r="Q14" s="63"/>
-      <c r="R14" s="63"/>
-      <c r="S14" s="63"/>
-      <c r="T14" s="63"/>
-      <c r="U14" s="63"/>
-      <c r="V14" s="63"/>
-      <c r="W14" s="63"/>
-      <c r="X14" s="64"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="66"/>
+      <c r="K14" s="66"/>
+      <c r="L14" s="66"/>
+      <c r="M14" s="66"/>
+      <c r="N14" s="66"/>
+      <c r="O14" s="66"/>
+      <c r="P14" s="66"/>
+      <c r="Q14" s="66"/>
+      <c r="R14" s="66"/>
+      <c r="S14" s="66"/>
+      <c r="T14" s="66"/>
+      <c r="U14" s="66"/>
+      <c r="V14" s="66"/>
+      <c r="W14" s="66"/>
+      <c r="X14" s="67"/>
     </row>
     <row r="15" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D15" s="65" t="s">
+      <c r="D15" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="E15" s="66"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="65">
+      <c r="E15" s="69"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="68">
         <v>0.1</v>
       </c>
-      <c r="H15" s="67"/>
-      <c r="I15" s="65">
+      <c r="H15" s="70"/>
+      <c r="I15" s="68">
         <v>0.2</v>
       </c>
-      <c r="J15" s="67"/>
-      <c r="K15" s="65">
+      <c r="J15" s="70"/>
+      <c r="K15" s="68">
         <v>0.3</v>
       </c>
-      <c r="L15" s="67"/>
-      <c r="M15" s="65">
+      <c r="L15" s="70"/>
+      <c r="M15" s="68">
         <v>0.4</v>
       </c>
-      <c r="N15" s="67"/>
-      <c r="O15" s="65">
+      <c r="N15" s="70"/>
+      <c r="O15" s="68">
         <v>0.5</v>
       </c>
-      <c r="P15" s="67"/>
-      <c r="Q15" s="65">
+      <c r="P15" s="70"/>
+      <c r="Q15" s="68">
         <v>0.6</v>
       </c>
-      <c r="R15" s="67"/>
-      <c r="S15" s="65">
+      <c r="R15" s="70"/>
+      <c r="S15" s="68">
         <v>0.7</v>
       </c>
-      <c r="T15" s="67"/>
-      <c r="U15" s="65">
+      <c r="T15" s="70"/>
+      <c r="U15" s="68">
         <v>0.8</v>
       </c>
-      <c r="V15" s="67"/>
-      <c r="W15" s="65">
+      <c r="V15" s="70"/>
+      <c r="W15" s="68">
         <v>0.9</v>
       </c>
-      <c r="X15" s="67"/>
+      <c r="X15" s="70"/>
     </row>
     <row r="16" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D16" s="8"/>
       <c r="E16" s="27"/>
       <c r="F16" s="9"/>
-      <c r="G16" s="48" t="s">
+      <c r="G16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="49"/>
-      <c r="I16" s="48" t="s">
+      <c r="H16" s="72"/>
+      <c r="I16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="J16" s="49"/>
-      <c r="K16" s="48" t="s">
+      <c r="J16" s="72"/>
+      <c r="K16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="L16" s="58"/>
-      <c r="M16" s="48" t="s">
+      <c r="L16" s="81"/>
+      <c r="M16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="N16" s="49"/>
-      <c r="O16" s="48" t="s">
+      <c r="N16" s="72"/>
+      <c r="O16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="P16" s="49"/>
-      <c r="Q16" s="48" t="s">
+      <c r="P16" s="72"/>
+      <c r="Q16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="R16" s="49"/>
-      <c r="S16" s="48" t="s">
+      <c r="R16" s="72"/>
+      <c r="S16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T16" s="49"/>
-      <c r="U16" s="50" t="s">
+      <c r="T16" s="72"/>
+      <c r="U16" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="V16" s="51"/>
-      <c r="W16" s="50" t="s">
+      <c r="V16" s="74"/>
+      <c r="W16" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="X16" s="51"/>
+      <c r="X16" s="74"/>
     </row>
     <row r="17" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D17" s="10"/>
@@ -3975,10 +4109,10 @@
       </c>
     </row>
     <row r="18" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D18" s="52" t="s">
+      <c r="D18" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="55">
+      <c r="E18" s="78">
         <v>0.3</v>
       </c>
       <c r="F18" s="29" t="s">
@@ -4040,8 +4174,8 @@
       </c>
     </row>
     <row r="19" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D19" s="53"/>
-      <c r="E19" s="56"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="79"/>
       <c r="F19" s="29" t="s">
         <v>13</v>
       </c>
@@ -4101,8 +4235,8 @@
       </c>
     </row>
     <row r="20" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D20" s="53"/>
-      <c r="E20" s="57"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="80"/>
       <c r="F20" s="29" t="s">
         <v>11</v>
       </c>
@@ -4162,8 +4296,8 @@
       </c>
     </row>
     <row r="21" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="53"/>
-      <c r="E21" s="55">
+      <c r="D21" s="76"/>
+      <c r="E21" s="78">
         <v>0.6</v>
       </c>
       <c r="F21" s="29" t="s">
@@ -4225,8 +4359,8 @@
       </c>
     </row>
     <row r="22" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D22" s="53"/>
-      <c r="E22" s="56"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="79"/>
       <c r="F22" s="29" t="s">
         <v>13</v>
       </c>
@@ -4286,8 +4420,8 @@
       </c>
     </row>
     <row r="23" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D23" s="53"/>
-      <c r="E23" s="57"/>
+      <c r="D23" s="76"/>
+      <c r="E23" s="80"/>
       <c r="F23" s="29" t="s">
         <v>11</v>
       </c>
@@ -4347,8 +4481,8 @@
       </c>
     </row>
     <row r="24" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="53"/>
-      <c r="E24" s="55">
+      <c r="D24" s="76"/>
+      <c r="E24" s="78">
         <v>0.9</v>
       </c>
       <c r="F24" s="29" t="s">
@@ -4410,8 +4544,8 @@
       </c>
     </row>
     <row r="25" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="53"/>
-      <c r="E25" s="56"/>
+      <c r="D25" s="76"/>
+      <c r="E25" s="79"/>
       <c r="F25" s="29" t="s">
         <v>13</v>
       </c>
@@ -4471,8 +4605,8 @@
       </c>
     </row>
     <row r="26" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="54"/>
-      <c r="E26" s="57"/>
+      <c r="D26" s="77"/>
+      <c r="E26" s="80"/>
       <c r="F26" s="29" t="s">
         <v>11</v>
       </c>
@@ -4533,6 +4667,16 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="G13:X14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="S15:T15"/>
+    <mergeCell ref="U15:V15"/>
     <mergeCell ref="D18:D26"/>
     <mergeCell ref="E18:E20"/>
     <mergeCell ref="E21:E23"/>
@@ -4547,16 +4691,6 @@
     <mergeCell ref="S16:T16"/>
     <mergeCell ref="U16:V16"/>
     <mergeCell ref="W16:X16"/>
-    <mergeCell ref="G13:X14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="S15:T15"/>
-    <mergeCell ref="U15:V15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4569,130 +4703,130 @@
   <sheetData>
     <row r="12" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="4:24" x14ac:dyDescent="0.2">
-      <c r="G13" s="59" t="s">
+      <c r="G13" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="60"/>
-      <c r="K13" s="60"/>
-      <c r="L13" s="60"/>
-      <c r="M13" s="60"/>
-      <c r="N13" s="60"/>
-      <c r="O13" s="60"/>
-      <c r="P13" s="60"/>
-      <c r="Q13" s="60"/>
-      <c r="R13" s="60"/>
-      <c r="S13" s="60"/>
-      <c r="T13" s="60"/>
-      <c r="U13" s="60"/>
-      <c r="V13" s="60"/>
-      <c r="W13" s="60"/>
-      <c r="X13" s="61"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="63"/>
+      <c r="L13" s="63"/>
+      <c r="M13" s="63"/>
+      <c r="N13" s="63"/>
+      <c r="O13" s="63"/>
+      <c r="P13" s="63"/>
+      <c r="Q13" s="63"/>
+      <c r="R13" s="63"/>
+      <c r="S13" s="63"/>
+      <c r="T13" s="63"/>
+      <c r="U13" s="63"/>
+      <c r="V13" s="63"/>
+      <c r="W13" s="63"/>
+      <c r="X13" s="64"/>
     </row>
     <row r="14" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G14" s="62"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="63"/>
-      <c r="K14" s="63"/>
-      <c r="L14" s="63"/>
-      <c r="M14" s="63"/>
-      <c r="N14" s="63"/>
-      <c r="O14" s="63"/>
-      <c r="P14" s="63"/>
-      <c r="Q14" s="63"/>
-      <c r="R14" s="63"/>
-      <c r="S14" s="63"/>
-      <c r="T14" s="63"/>
-      <c r="U14" s="63"/>
-      <c r="V14" s="63"/>
-      <c r="W14" s="63"/>
-      <c r="X14" s="64"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="66"/>
+      <c r="K14" s="66"/>
+      <c r="L14" s="66"/>
+      <c r="M14" s="66"/>
+      <c r="N14" s="66"/>
+      <c r="O14" s="66"/>
+      <c r="P14" s="66"/>
+      <c r="Q14" s="66"/>
+      <c r="R14" s="66"/>
+      <c r="S14" s="66"/>
+      <c r="T14" s="66"/>
+      <c r="U14" s="66"/>
+      <c r="V14" s="66"/>
+      <c r="W14" s="66"/>
+      <c r="X14" s="67"/>
     </row>
     <row r="15" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D15" s="65" t="s">
+      <c r="D15" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="E15" s="66"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="65">
+      <c r="E15" s="69"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="68">
         <v>0.1</v>
       </c>
-      <c r="H15" s="67"/>
-      <c r="I15" s="65">
+      <c r="H15" s="70"/>
+      <c r="I15" s="68">
         <v>0.2</v>
       </c>
-      <c r="J15" s="67"/>
-      <c r="K15" s="65">
+      <c r="J15" s="70"/>
+      <c r="K15" s="68">
         <v>0.3</v>
       </c>
-      <c r="L15" s="67"/>
-      <c r="M15" s="65">
+      <c r="L15" s="70"/>
+      <c r="M15" s="68">
         <v>0.4</v>
       </c>
-      <c r="N15" s="67"/>
-      <c r="O15" s="65">
+      <c r="N15" s="70"/>
+      <c r="O15" s="68">
         <v>0.5</v>
       </c>
-      <c r="P15" s="67"/>
-      <c r="Q15" s="65">
+      <c r="P15" s="70"/>
+      <c r="Q15" s="68">
         <v>0.6</v>
       </c>
-      <c r="R15" s="67"/>
-      <c r="S15" s="65">
+      <c r="R15" s="70"/>
+      <c r="S15" s="68">
         <v>0.7</v>
       </c>
-      <c r="T15" s="67"/>
-      <c r="U15" s="65">
+      <c r="T15" s="70"/>
+      <c r="U15" s="68">
         <v>0.8</v>
       </c>
-      <c r="V15" s="67"/>
-      <c r="W15" s="65">
+      <c r="V15" s="70"/>
+      <c r="W15" s="68">
         <v>0.9</v>
       </c>
-      <c r="X15" s="67"/>
+      <c r="X15" s="70"/>
     </row>
     <row r="16" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D16" s="8"/>
       <c r="E16" s="27"/>
       <c r="F16" s="9"/>
-      <c r="G16" s="48" t="s">
+      <c r="G16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="49"/>
-      <c r="I16" s="48" t="s">
+      <c r="H16" s="72"/>
+      <c r="I16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="J16" s="49"/>
-      <c r="K16" s="48" t="s">
+      <c r="J16" s="72"/>
+      <c r="K16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="L16" s="58"/>
-      <c r="M16" s="48" t="s">
+      <c r="L16" s="81"/>
+      <c r="M16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="N16" s="49"/>
-      <c r="O16" s="48" t="s">
+      <c r="N16" s="72"/>
+      <c r="O16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="P16" s="49"/>
-      <c r="Q16" s="48" t="s">
+      <c r="P16" s="72"/>
+      <c r="Q16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="R16" s="49"/>
-      <c r="S16" s="48" t="s">
+      <c r="R16" s="72"/>
+      <c r="S16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T16" s="49"/>
-      <c r="U16" s="50" t="s">
+      <c r="T16" s="72"/>
+      <c r="U16" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="V16" s="51"/>
-      <c r="W16" s="50" t="s">
+      <c r="V16" s="74"/>
+      <c r="W16" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="X16" s="51"/>
+      <c r="X16" s="74"/>
     </row>
     <row r="17" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D17" s="10"/>
@@ -4754,10 +4888,10 @@
       </c>
     </row>
     <row r="18" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D18" s="52" t="s">
+      <c r="D18" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="55">
+      <c r="E18" s="78">
         <v>0.3</v>
       </c>
       <c r="F18" s="29" t="s">
@@ -4819,8 +4953,8 @@
       </c>
     </row>
     <row r="19" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D19" s="53"/>
-      <c r="E19" s="56"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="79"/>
       <c r="F19" s="29" t="s">
         <v>13</v>
       </c>
@@ -4880,8 +5014,8 @@
       </c>
     </row>
     <row r="20" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D20" s="53"/>
-      <c r="E20" s="57"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="80"/>
       <c r="F20" s="29" t="s">
         <v>11</v>
       </c>
@@ -4941,8 +5075,8 @@
       </c>
     </row>
     <row r="21" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="53"/>
-      <c r="E21" s="55">
+      <c r="D21" s="76"/>
+      <c r="E21" s="78">
         <v>0.6</v>
       </c>
       <c r="F21" s="29" t="s">
@@ -5004,8 +5138,8 @@
       </c>
     </row>
     <row r="22" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D22" s="53"/>
-      <c r="E22" s="56"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="79"/>
       <c r="F22" s="29" t="s">
         <v>13</v>
       </c>
@@ -5065,8 +5199,8 @@
       </c>
     </row>
     <row r="23" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D23" s="53"/>
-      <c r="E23" s="57"/>
+      <c r="D23" s="76"/>
+      <c r="E23" s="80"/>
       <c r="F23" s="29" t="s">
         <v>11</v>
       </c>
@@ -5126,8 +5260,8 @@
       </c>
     </row>
     <row r="24" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="53"/>
-      <c r="E24" s="55">
+      <c r="D24" s="76"/>
+      <c r="E24" s="78">
         <v>0.9</v>
       </c>
       <c r="F24" s="29" t="s">
@@ -5189,8 +5323,8 @@
       </c>
     </row>
     <row r="25" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="53"/>
-      <c r="E25" s="56"/>
+      <c r="D25" s="76"/>
+      <c r="E25" s="79"/>
       <c r="F25" s="29" t="s">
         <v>13</v>
       </c>
@@ -5250,8 +5384,8 @@
       </c>
     </row>
     <row r="26" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="54"/>
-      <c r="E26" s="57"/>
+      <c r="D26" s="77"/>
+      <c r="E26" s="80"/>
       <c r="F26" s="29" t="s">
         <v>11</v>
       </c>
@@ -5312,6 +5446,16 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="G13:X14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="S15:T15"/>
+    <mergeCell ref="U15:V15"/>
     <mergeCell ref="D18:D26"/>
     <mergeCell ref="E18:E20"/>
     <mergeCell ref="E21:E23"/>
@@ -5326,16 +5470,6 @@
     <mergeCell ref="S16:T16"/>
     <mergeCell ref="U16:V16"/>
     <mergeCell ref="W16:X16"/>
-    <mergeCell ref="G13:X14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="S15:T15"/>
-    <mergeCell ref="U15:V15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5348,130 +5482,130 @@
   <sheetData>
     <row r="12" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="4:24" x14ac:dyDescent="0.2">
-      <c r="G13" s="59" t="s">
+      <c r="G13" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="60"/>
-      <c r="K13" s="60"/>
-      <c r="L13" s="60"/>
-      <c r="M13" s="60"/>
-      <c r="N13" s="60"/>
-      <c r="O13" s="60"/>
-      <c r="P13" s="60"/>
-      <c r="Q13" s="60"/>
-      <c r="R13" s="60"/>
-      <c r="S13" s="60"/>
-      <c r="T13" s="60"/>
-      <c r="U13" s="60"/>
-      <c r="V13" s="60"/>
-      <c r="W13" s="60"/>
-      <c r="X13" s="61"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="63"/>
+      <c r="L13" s="63"/>
+      <c r="M13" s="63"/>
+      <c r="N13" s="63"/>
+      <c r="O13" s="63"/>
+      <c r="P13" s="63"/>
+      <c r="Q13" s="63"/>
+      <c r="R13" s="63"/>
+      <c r="S13" s="63"/>
+      <c r="T13" s="63"/>
+      <c r="U13" s="63"/>
+      <c r="V13" s="63"/>
+      <c r="W13" s="63"/>
+      <c r="X13" s="64"/>
     </row>
     <row r="14" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G14" s="62"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="63"/>
-      <c r="K14" s="63"/>
-      <c r="L14" s="63"/>
-      <c r="M14" s="63"/>
-      <c r="N14" s="63"/>
-      <c r="O14" s="63"/>
-      <c r="P14" s="63"/>
-      <c r="Q14" s="63"/>
-      <c r="R14" s="63"/>
-      <c r="S14" s="63"/>
-      <c r="T14" s="63"/>
-      <c r="U14" s="63"/>
-      <c r="V14" s="63"/>
-      <c r="W14" s="63"/>
-      <c r="X14" s="64"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="66"/>
+      <c r="K14" s="66"/>
+      <c r="L14" s="66"/>
+      <c r="M14" s="66"/>
+      <c r="N14" s="66"/>
+      <c r="O14" s="66"/>
+      <c r="P14" s="66"/>
+      <c r="Q14" s="66"/>
+      <c r="R14" s="66"/>
+      <c r="S14" s="66"/>
+      <c r="T14" s="66"/>
+      <c r="U14" s="66"/>
+      <c r="V14" s="66"/>
+      <c r="W14" s="66"/>
+      <c r="X14" s="67"/>
     </row>
     <row r="15" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D15" s="65" t="s">
+      <c r="D15" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="E15" s="66"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="65">
+      <c r="E15" s="69"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="68">
         <v>0.1</v>
       </c>
-      <c r="H15" s="67"/>
-      <c r="I15" s="65">
+      <c r="H15" s="70"/>
+      <c r="I15" s="68">
         <v>0.2</v>
       </c>
-      <c r="J15" s="67"/>
-      <c r="K15" s="65">
+      <c r="J15" s="70"/>
+      <c r="K15" s="68">
         <v>0.3</v>
       </c>
-      <c r="L15" s="67"/>
-      <c r="M15" s="65">
+      <c r="L15" s="70"/>
+      <c r="M15" s="68">
         <v>0.4</v>
       </c>
-      <c r="N15" s="67"/>
-      <c r="O15" s="65">
+      <c r="N15" s="70"/>
+      <c r="O15" s="68">
         <v>0.5</v>
       </c>
-      <c r="P15" s="67"/>
-      <c r="Q15" s="65">
+      <c r="P15" s="70"/>
+      <c r="Q15" s="68">
         <v>0.6</v>
       </c>
-      <c r="R15" s="67"/>
-      <c r="S15" s="65">
+      <c r="R15" s="70"/>
+      <c r="S15" s="68">
         <v>0.7</v>
       </c>
-      <c r="T15" s="67"/>
-      <c r="U15" s="65">
+      <c r="T15" s="70"/>
+      <c r="U15" s="68">
         <v>0.8</v>
       </c>
-      <c r="V15" s="67"/>
-      <c r="W15" s="65">
+      <c r="V15" s="70"/>
+      <c r="W15" s="68">
         <v>0.9</v>
       </c>
-      <c r="X15" s="67"/>
+      <c r="X15" s="70"/>
     </row>
     <row r="16" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D16" s="8"/>
       <c r="E16" s="27"/>
       <c r="F16" s="9"/>
-      <c r="G16" s="48" t="s">
+      <c r="G16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="49"/>
-      <c r="I16" s="48" t="s">
+      <c r="H16" s="72"/>
+      <c r="I16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="J16" s="49"/>
-      <c r="K16" s="48" t="s">
+      <c r="J16" s="72"/>
+      <c r="K16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="L16" s="58"/>
-      <c r="M16" s="48" t="s">
+      <c r="L16" s="81"/>
+      <c r="M16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="N16" s="49"/>
-      <c r="O16" s="48" t="s">
+      <c r="N16" s="72"/>
+      <c r="O16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="P16" s="49"/>
-      <c r="Q16" s="48" t="s">
+      <c r="P16" s="72"/>
+      <c r="Q16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="R16" s="49"/>
-      <c r="S16" s="48" t="s">
+      <c r="R16" s="72"/>
+      <c r="S16" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T16" s="49"/>
-      <c r="U16" s="50" t="s">
+      <c r="T16" s="72"/>
+      <c r="U16" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="V16" s="51"/>
-      <c r="W16" s="50" t="s">
+      <c r="V16" s="74"/>
+      <c r="W16" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="X16" s="51"/>
+      <c r="X16" s="74"/>
     </row>
     <row r="17" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D17" s="10"/>
@@ -5533,10 +5667,10 @@
       </c>
     </row>
     <row r="18" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D18" s="52" t="s">
+      <c r="D18" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="55">
+      <c r="E18" s="78">
         <v>0.3</v>
       </c>
       <c r="F18" s="29" t="s">
@@ -5598,8 +5732,8 @@
       </c>
     </row>
     <row r="19" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D19" s="53"/>
-      <c r="E19" s="56"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="79"/>
       <c r="F19" s="29" t="s">
         <v>13</v>
       </c>
@@ -5659,8 +5793,8 @@
       </c>
     </row>
     <row r="20" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D20" s="53"/>
-      <c r="E20" s="57"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="80"/>
       <c r="F20" s="29" t="s">
         <v>11</v>
       </c>
@@ -5720,8 +5854,8 @@
       </c>
     </row>
     <row r="21" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="53"/>
-      <c r="E21" s="55">
+      <c r="D21" s="76"/>
+      <c r="E21" s="78">
         <v>0.6</v>
       </c>
       <c r="F21" s="29" t="s">
@@ -5783,8 +5917,8 @@
       </c>
     </row>
     <row r="22" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D22" s="53"/>
-      <c r="E22" s="56"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="79"/>
       <c r="F22" s="29" t="s">
         <v>13</v>
       </c>
@@ -5844,8 +5978,8 @@
       </c>
     </row>
     <row r="23" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D23" s="53"/>
-      <c r="E23" s="57"/>
+      <c r="D23" s="76"/>
+      <c r="E23" s="80"/>
       <c r="F23" s="29" t="s">
         <v>11</v>
       </c>
@@ -5905,8 +6039,8 @@
       </c>
     </row>
     <row r="24" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="53"/>
-      <c r="E24" s="55">
+      <c r="D24" s="76"/>
+      <c r="E24" s="78">
         <v>0.9</v>
       </c>
       <c r="F24" s="29" t="s">
@@ -5968,8 +6102,8 @@
       </c>
     </row>
     <row r="25" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="53"/>
-      <c r="E25" s="56"/>
+      <c r="D25" s="76"/>
+      <c r="E25" s="79"/>
       <c r="F25" s="29" t="s">
         <v>13</v>
       </c>
@@ -6029,8 +6163,8 @@
       </c>
     </row>
     <row r="26" spans="4:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="54"/>
-      <c r="E26" s="57"/>
+      <c r="D26" s="77"/>
+      <c r="E26" s="80"/>
       <c r="F26" s="29" t="s">
         <v>11</v>
       </c>
@@ -6091,6 +6225,16 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="G13:X14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="S15:T15"/>
+    <mergeCell ref="U15:V15"/>
     <mergeCell ref="D18:D26"/>
     <mergeCell ref="E18:E20"/>
     <mergeCell ref="E21:E23"/>
@@ -6105,16 +6249,6 @@
     <mergeCell ref="S16:T16"/>
     <mergeCell ref="U16:V16"/>
     <mergeCell ref="W16:X16"/>
-    <mergeCell ref="G13:X14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="S15:T15"/>
-    <mergeCell ref="U15:V15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6131,35 +6265,35 @@
     <row r="10" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="5:9" x14ac:dyDescent="0.2">
       <c r="E11" s="32"/>
-      <c r="F11" s="71" t="s">
+      <c r="F11" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="73"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="84"/>
     </row>
     <row r="12" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E12" s="32"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="76"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="86"/>
+      <c r="H12" s="86"/>
+      <c r="I12" s="87"/>
     </row>
     <row r="13" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E13" s="32"/>
       <c r="F13" s="33"/>
       <c r="G13" s="34"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="78"/>
+      <c r="H13" s="88"/>
+      <c r="I13" s="89"/>
     </row>
     <row r="14" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E14" s="32"/>
       <c r="F14" s="35"/>
       <c r="G14" s="36"/>
-      <c r="H14" s="50" t="s">
+      <c r="H14" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="79"/>
+      <c r="I14" s="90"/>
     </row>
     <row r="15" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E15" s="32"/>
@@ -6173,10 +6307,10 @@
       </c>
     </row>
     <row r="16" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E16" s="80" t="s">
+      <c r="E16" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="83" t="s">
+      <c r="F16" s="94" t="s">
         <v>10</v>
       </c>
       <c r="G16" s="29" t="s">
@@ -6190,8 +6324,8 @@
       </c>
     </row>
     <row r="17" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E17" s="81"/>
-      <c r="F17" s="69"/>
+      <c r="E17" s="92"/>
+      <c r="F17" s="95"/>
       <c r="G17" s="29" t="s">
         <v>13</v>
       </c>
@@ -6203,8 +6337,8 @@
       </c>
     </row>
     <row r="18" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E18" s="81"/>
-      <c r="F18" s="69"/>
+      <c r="E18" s="92"/>
+      <c r="F18" s="95"/>
       <c r="G18" s="29" t="s">
         <v>11</v>
       </c>
@@ -6216,8 +6350,8 @@
       </c>
     </row>
     <row r="19" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E19" s="81"/>
-      <c r="F19" s="69"/>
+      <c r="E19" s="92"/>
+      <c r="F19" s="95"/>
       <c r="G19" s="47" t="s">
         <v>17</v>
       </c>
@@ -6229,8 +6363,8 @@
       </c>
     </row>
     <row r="20" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E20" s="81"/>
-      <c r="F20" s="69"/>
+      <c r="E20" s="92"/>
+      <c r="F20" s="95"/>
       <c r="G20" s="47" t="s">
         <v>18</v>
       </c>
@@ -6242,8 +6376,8 @@
       </c>
     </row>
     <row r="21" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E21" s="81"/>
-      <c r="F21" s="69"/>
+      <c r="E21" s="92"/>
+      <c r="F21" s="95"/>
       <c r="G21" s="47" t="s">
         <v>19</v>
       </c>
@@ -6255,8 +6389,8 @@
       </c>
     </row>
     <row r="22" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E22" s="81"/>
-      <c r="F22" s="69"/>
+      <c r="E22" s="92"/>
+      <c r="F22" s="95"/>
       <c r="G22" s="47" t="s">
         <v>20</v>
       </c>
@@ -6268,8 +6402,8 @@
       </c>
     </row>
     <row r="23" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E23" s="81"/>
-      <c r="F23" s="69"/>
+      <c r="E23" s="92"/>
+      <c r="F23" s="95"/>
       <c r="G23" s="47" t="s">
         <v>21</v>
       </c>
@@ -6281,8 +6415,8 @@
       </c>
     </row>
     <row r="24" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E24" s="81"/>
-      <c r="F24" s="69"/>
+      <c r="E24" s="92"/>
+      <c r="F24" s="95"/>
       <c r="G24" s="47" t="s">
         <v>22</v>
       </c>
@@ -6294,8 +6428,8 @@
       </c>
     </row>
     <row r="25" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E25" s="81"/>
-      <c r="F25" s="69"/>
+      <c r="E25" s="92"/>
+      <c r="F25" s="95"/>
       <c r="G25" s="47" t="s">
         <v>23</v>
       </c>
@@ -6307,8 +6441,8 @@
       </c>
     </row>
     <row r="26" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E26" s="81"/>
-      <c r="F26" s="70"/>
+      <c r="E26" s="92"/>
+      <c r="F26" s="96"/>
       <c r="G26" s="47" t="s">
         <v>24</v>
       </c>
@@ -6320,8 +6454,8 @@
       </c>
     </row>
     <row r="27" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E27" s="81"/>
-      <c r="F27" s="68" t="s">
+      <c r="E27" s="92"/>
+      <c r="F27" s="97" t="s">
         <v>9</v>
       </c>
       <c r="G27" s="29" t="s">
@@ -6335,8 +6469,8 @@
       </c>
     </row>
     <row r="28" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E28" s="81"/>
-      <c r="F28" s="69"/>
+      <c r="E28" s="92"/>
+      <c r="F28" s="95"/>
       <c r="G28" s="29" t="s">
         <v>13</v>
       </c>
@@ -6348,8 +6482,8 @@
       </c>
     </row>
     <row r="29" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E29" s="81"/>
-      <c r="F29" s="69"/>
+      <c r="E29" s="92"/>
+      <c r="F29" s="95"/>
       <c r="G29" s="29" t="s">
         <v>11</v>
       </c>
@@ -6361,8 +6495,8 @@
       </c>
     </row>
     <row r="30" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E30" s="81"/>
-      <c r="F30" s="69"/>
+      <c r="E30" s="92"/>
+      <c r="F30" s="95"/>
       <c r="G30" s="47" t="s">
         <v>17</v>
       </c>
@@ -6374,8 +6508,8 @@
       </c>
     </row>
     <row r="31" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E31" s="81"/>
-      <c r="F31" s="69"/>
+      <c r="E31" s="92"/>
+      <c r="F31" s="95"/>
       <c r="G31" s="47" t="s">
         <v>18</v>
       </c>
@@ -6387,8 +6521,8 @@
       </c>
     </row>
     <row r="32" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E32" s="81"/>
-      <c r="F32" s="69"/>
+      <c r="E32" s="92"/>
+      <c r="F32" s="95"/>
       <c r="G32" s="47" t="s">
         <v>19</v>
       </c>
@@ -6400,8 +6534,8 @@
       </c>
     </row>
     <row r="33" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E33" s="81"/>
-      <c r="F33" s="69"/>
+      <c r="E33" s="92"/>
+      <c r="F33" s="95"/>
       <c r="G33" s="47" t="s">
         <v>20</v>
       </c>
@@ -6413,8 +6547,8 @@
       </c>
     </row>
     <row r="34" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E34" s="81"/>
-      <c r="F34" s="69"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="95"/>
       <c r="G34" s="47" t="s">
         <v>21</v>
       </c>
@@ -6426,8 +6560,8 @@
       </c>
     </row>
     <row r="35" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E35" s="81"/>
-      <c r="F35" s="69"/>
+      <c r="E35" s="92"/>
+      <c r="F35" s="95"/>
       <c r="G35" s="47" t="s">
         <v>22</v>
       </c>
@@ -6439,8 +6573,8 @@
       </c>
     </row>
     <row r="36" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E36" s="81"/>
-      <c r="F36" s="69"/>
+      <c r="E36" s="92"/>
+      <c r="F36" s="95"/>
       <c r="G36" s="47" t="s">
         <v>23</v>
       </c>
@@ -6452,8 +6586,8 @@
       </c>
     </row>
     <row r="37" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E37" s="81"/>
-      <c r="F37" s="70"/>
+      <c r="E37" s="92"/>
+      <c r="F37" s="96"/>
       <c r="G37" s="47" t="s">
         <v>24</v>
       </c>
@@ -6465,8 +6599,8 @@
       </c>
     </row>
     <row r="38" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E38" s="81"/>
-      <c r="F38" s="68" t="s">
+      <c r="E38" s="92"/>
+      <c r="F38" s="97" t="s">
         <v>8</v>
       </c>
       <c r="G38" s="29" t="s">
@@ -6480,8 +6614,8 @@
       </c>
     </row>
     <row r="39" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E39" s="81"/>
-      <c r="F39" s="69"/>
+      <c r="E39" s="92"/>
+      <c r="F39" s="95"/>
       <c r="G39" s="29" t="s">
         <v>13</v>
       </c>
@@ -6493,8 +6627,8 @@
       </c>
     </row>
     <row r="40" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E40" s="81"/>
-      <c r="F40" s="69"/>
+      <c r="E40" s="92"/>
+      <c r="F40" s="95"/>
       <c r="G40" s="29" t="s">
         <v>11</v>
       </c>
@@ -6506,8 +6640,8 @@
       </c>
     </row>
     <row r="41" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E41" s="81"/>
-      <c r="F41" s="69"/>
+      <c r="E41" s="92"/>
+      <c r="F41" s="95"/>
       <c r="G41" s="47" t="s">
         <v>17</v>
       </c>
@@ -6519,8 +6653,8 @@
       </c>
     </row>
     <row r="42" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E42" s="81"/>
-      <c r="F42" s="69"/>
+      <c r="E42" s="92"/>
+      <c r="F42" s="95"/>
       <c r="G42" s="47" t="s">
         <v>18</v>
       </c>
@@ -6532,8 +6666,8 @@
       </c>
     </row>
     <row r="43" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E43" s="81"/>
-      <c r="F43" s="69"/>
+      <c r="E43" s="92"/>
+      <c r="F43" s="95"/>
       <c r="G43" s="47" t="s">
         <v>19</v>
       </c>
@@ -6545,8 +6679,8 @@
       </c>
     </row>
     <row r="44" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E44" s="81"/>
-      <c r="F44" s="69"/>
+      <c r="E44" s="92"/>
+      <c r="F44" s="95"/>
       <c r="G44" s="47" t="s">
         <v>20</v>
       </c>
@@ -6558,8 +6692,8 @@
       </c>
     </row>
     <row r="45" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E45" s="81"/>
-      <c r="F45" s="69"/>
+      <c r="E45" s="92"/>
+      <c r="F45" s="95"/>
       <c r="G45" s="47" t="s">
         <v>21</v>
       </c>
@@ -6571,8 +6705,8 @@
       </c>
     </row>
     <row r="46" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E46" s="81"/>
-      <c r="F46" s="69"/>
+      <c r="E46" s="92"/>
+      <c r="F46" s="95"/>
       <c r="G46" s="47" t="s">
         <v>22</v>
       </c>
@@ -6584,8 +6718,8 @@
       </c>
     </row>
     <row r="47" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E47" s="81"/>
-      <c r="F47" s="69"/>
+      <c r="E47" s="92"/>
+      <c r="F47" s="95"/>
       <c r="G47" s="47" t="s">
         <v>23</v>
       </c>
@@ -6597,8 +6731,8 @@
       </c>
     </row>
     <row r="48" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E48" s="81"/>
-      <c r="F48" s="70"/>
+      <c r="E48" s="92"/>
+      <c r="F48" s="96"/>
       <c r="G48" s="47" t="s">
         <v>24</v>
       </c>
@@ -6610,8 +6744,8 @@
       </c>
     </row>
     <row r="49" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E49" s="81"/>
-      <c r="F49" s="68" t="s">
+      <c r="E49" s="92"/>
+      <c r="F49" s="97" t="s">
         <v>7</v>
       </c>
       <c r="G49" s="29" t="s">
@@ -6625,8 +6759,8 @@
       </c>
     </row>
     <row r="50" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E50" s="81"/>
-      <c r="F50" s="69"/>
+      <c r="E50" s="92"/>
+      <c r="F50" s="95"/>
       <c r="G50" s="29" t="s">
         <v>13</v>
       </c>
@@ -6638,8 +6772,8 @@
       </c>
     </row>
     <row r="51" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E51" s="81"/>
-      <c r="F51" s="69"/>
+      <c r="E51" s="92"/>
+      <c r="F51" s="95"/>
       <c r="G51" s="29" t="s">
         <v>11</v>
       </c>
@@ -6651,8 +6785,8 @@
       </c>
     </row>
     <row r="52" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E52" s="81"/>
-      <c r="F52" s="69"/>
+      <c r="E52" s="92"/>
+      <c r="F52" s="95"/>
       <c r="G52" s="47" t="s">
         <v>17</v>
       </c>
@@ -6664,8 +6798,8 @@
       </c>
     </row>
     <row r="53" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E53" s="81"/>
-      <c r="F53" s="69"/>
+      <c r="E53" s="92"/>
+      <c r="F53" s="95"/>
       <c r="G53" s="47" t="s">
         <v>18</v>
       </c>
@@ -6677,8 +6811,8 @@
       </c>
     </row>
     <row r="54" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E54" s="81"/>
-      <c r="F54" s="69"/>
+      <c r="E54" s="92"/>
+      <c r="F54" s="95"/>
       <c r="G54" s="47" t="s">
         <v>19</v>
       </c>
@@ -6690,8 +6824,8 @@
       </c>
     </row>
     <row r="55" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E55" s="81"/>
-      <c r="F55" s="69"/>
+      <c r="E55" s="92"/>
+      <c r="F55" s="95"/>
       <c r="G55" s="47" t="s">
         <v>20</v>
       </c>
@@ -6703,8 +6837,8 @@
       </c>
     </row>
     <row r="56" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E56" s="81"/>
-      <c r="F56" s="69"/>
+      <c r="E56" s="92"/>
+      <c r="F56" s="95"/>
       <c r="G56" s="47" t="s">
         <v>21</v>
       </c>
@@ -6716,8 +6850,8 @@
       </c>
     </row>
     <row r="57" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E57" s="81"/>
-      <c r="F57" s="69"/>
+      <c r="E57" s="92"/>
+      <c r="F57" s="95"/>
       <c r="G57" s="47" t="s">
         <v>22</v>
       </c>
@@ -6729,8 +6863,8 @@
       </c>
     </row>
     <row r="58" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E58" s="81"/>
-      <c r="F58" s="69"/>
+      <c r="E58" s="92"/>
+      <c r="F58" s="95"/>
       <c r="G58" s="47" t="s">
         <v>23</v>
       </c>
@@ -6742,8 +6876,8 @@
       </c>
     </row>
     <row r="59" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E59" s="81"/>
-      <c r="F59" s="70"/>
+      <c r="E59" s="92"/>
+      <c r="F59" s="96"/>
       <c r="G59" s="47" t="s">
         <v>24</v>
       </c>
@@ -6755,8 +6889,8 @@
       </c>
     </row>
     <row r="60" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E60" s="81"/>
-      <c r="F60" s="68" t="s">
+      <c r="E60" s="92"/>
+      <c r="F60" s="97" t="s">
         <v>6</v>
       </c>
       <c r="G60" s="29" t="s">
@@ -6770,8 +6904,8 @@
       </c>
     </row>
     <row r="61" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E61" s="81"/>
-      <c r="F61" s="69"/>
+      <c r="E61" s="92"/>
+      <c r="F61" s="95"/>
       <c r="G61" s="29" t="s">
         <v>13</v>
       </c>
@@ -6783,8 +6917,8 @@
       </c>
     </row>
     <row r="62" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E62" s="81"/>
-      <c r="F62" s="69"/>
+      <c r="E62" s="92"/>
+      <c r="F62" s="95"/>
       <c r="G62" s="29" t="s">
         <v>11</v>
       </c>
@@ -6796,8 +6930,8 @@
       </c>
     </row>
     <row r="63" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E63" s="81"/>
-      <c r="F63" s="69"/>
+      <c r="E63" s="92"/>
+      <c r="F63" s="95"/>
       <c r="G63" s="47" t="s">
         <v>17</v>
       </c>
@@ -6809,8 +6943,8 @@
       </c>
     </row>
     <row r="64" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E64" s="81"/>
-      <c r="F64" s="69"/>
+      <c r="E64" s="92"/>
+      <c r="F64" s="95"/>
       <c r="G64" s="47" t="s">
         <v>18</v>
       </c>
@@ -6822,8 +6956,8 @@
       </c>
     </row>
     <row r="65" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E65" s="81"/>
-      <c r="F65" s="69"/>
+      <c r="E65" s="92"/>
+      <c r="F65" s="95"/>
       <c r="G65" s="47" t="s">
         <v>19</v>
       </c>
@@ -6835,8 +6969,8 @@
       </c>
     </row>
     <row r="66" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E66" s="81"/>
-      <c r="F66" s="69"/>
+      <c r="E66" s="92"/>
+      <c r="F66" s="95"/>
       <c r="G66" s="47" t="s">
         <v>20</v>
       </c>
@@ -6848,8 +6982,8 @@
       </c>
     </row>
     <row r="67" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E67" s="81"/>
-      <c r="F67" s="69"/>
+      <c r="E67" s="92"/>
+      <c r="F67" s="95"/>
       <c r="G67" s="47" t="s">
         <v>21</v>
       </c>
@@ -6861,8 +6995,8 @@
       </c>
     </row>
     <row r="68" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E68" s="81"/>
-      <c r="F68" s="69"/>
+      <c r="E68" s="92"/>
+      <c r="F68" s="95"/>
       <c r="G68" s="47" t="s">
         <v>22</v>
       </c>
@@ -6874,8 +7008,8 @@
       </c>
     </row>
     <row r="69" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E69" s="81"/>
-      <c r="F69" s="69"/>
+      <c r="E69" s="92"/>
+      <c r="F69" s="95"/>
       <c r="G69" s="47" t="s">
         <v>23</v>
       </c>
@@ -6887,8 +7021,8 @@
       </c>
     </row>
     <row r="70" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E70" s="81"/>
-      <c r="F70" s="70"/>
+      <c r="E70" s="92"/>
+      <c r="F70" s="96"/>
       <c r="G70" s="47" t="s">
         <v>24</v>
       </c>
@@ -6900,8 +7034,8 @@
       </c>
     </row>
     <row r="71" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E71" s="81"/>
-      <c r="F71" s="68" t="s">
+      <c r="E71" s="92"/>
+      <c r="F71" s="97" t="s">
         <v>16</v>
       </c>
       <c r="G71" s="29" t="s">
@@ -6915,8 +7049,8 @@
       </c>
     </row>
     <row r="72" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E72" s="81"/>
-      <c r="F72" s="69"/>
+      <c r="E72" s="92"/>
+      <c r="F72" s="95"/>
       <c r="G72" s="29" t="s">
         <v>13</v>
       </c>
@@ -6928,8 +7062,8 @@
       </c>
     </row>
     <row r="73" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E73" s="81"/>
-      <c r="F73" s="69"/>
+      <c r="E73" s="92"/>
+      <c r="F73" s="95"/>
       <c r="G73" s="29" t="s">
         <v>11</v>
       </c>
@@ -6941,8 +7075,8 @@
       </c>
     </row>
     <row r="74" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E74" s="81"/>
-      <c r="F74" s="69"/>
+      <c r="E74" s="92"/>
+      <c r="F74" s="95"/>
       <c r="G74" s="47" t="s">
         <v>17</v>
       </c>
@@ -6954,8 +7088,8 @@
       </c>
     </row>
     <row r="75" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E75" s="81"/>
-      <c r="F75" s="69"/>
+      <c r="E75" s="92"/>
+      <c r="F75" s="95"/>
       <c r="G75" s="47" t="s">
         <v>18</v>
       </c>
@@ -6967,8 +7101,8 @@
       </c>
     </row>
     <row r="76" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E76" s="81"/>
-      <c r="F76" s="69"/>
+      <c r="E76" s="92"/>
+      <c r="F76" s="95"/>
       <c r="G76" s="47" t="s">
         <v>19</v>
       </c>
@@ -6980,8 +7114,8 @@
       </c>
     </row>
     <row r="77" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E77" s="81"/>
-      <c r="F77" s="69"/>
+      <c r="E77" s="92"/>
+      <c r="F77" s="95"/>
       <c r="G77" s="47" t="s">
         <v>20</v>
       </c>
@@ -6993,8 +7127,8 @@
       </c>
     </row>
     <row r="78" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E78" s="81"/>
-      <c r="F78" s="69"/>
+      <c r="E78" s="92"/>
+      <c r="F78" s="95"/>
       <c r="G78" s="47" t="s">
         <v>21</v>
       </c>
@@ -7006,8 +7140,8 @@
       </c>
     </row>
     <row r="79" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E79" s="81"/>
-      <c r="F79" s="69"/>
+      <c r="E79" s="92"/>
+      <c r="F79" s="95"/>
       <c r="G79" s="47" t="s">
         <v>22</v>
       </c>
@@ -7019,8 +7153,8 @@
       </c>
     </row>
     <row r="80" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E80" s="81"/>
-      <c r="F80" s="69"/>
+      <c r="E80" s="92"/>
+      <c r="F80" s="95"/>
       <c r="G80" s="47" t="s">
         <v>23</v>
       </c>
@@ -7032,8 +7166,8 @@
       </c>
     </row>
     <row r="81" spans="5:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E81" s="82"/>
-      <c r="F81" s="70"/>
+      <c r="E81" s="93"/>
+      <c r="F81" s="96"/>
       <c r="G81" s="47" t="s">
         <v>24</v>
       </c>
@@ -7046,6 +7180,9 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="F11:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
     <mergeCell ref="E16:E81"/>
     <mergeCell ref="F16:F26"/>
     <mergeCell ref="F27:F37"/>
@@ -7053,9 +7190,891 @@
     <mergeCell ref="F49:F59"/>
     <mergeCell ref="F60:F70"/>
     <mergeCell ref="F71:F81"/>
-    <mergeCell ref="F11:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2796DCB5-8F97-184D-90B6-E1EE46017DC9}">
+  <dimension ref="F7:J78"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="7" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="6:10" x14ac:dyDescent="0.2">
+      <c r="G8" s="103" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="104"/>
+      <c r="I8" s="104"/>
+      <c r="J8" s="105"/>
+    </row>
+    <row r="9" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G9" s="106"/>
+      <c r="H9" s="107"/>
+      <c r="I9" s="107"/>
+      <c r="J9" s="108"/>
+    </row>
+    <row r="10" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G10" s="48"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="109"/>
+      <c r="J10" s="110"/>
+    </row>
+    <row r="11" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G11" s="50"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="71" t="s">
+        <v>3</v>
+      </c>
+      <c r="J11" s="72"/>
+    </row>
+    <row r="12" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G12" s="52"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F13" s="98" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="101" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="54">
+        <v>0</v>
+      </c>
+      <c r="J13" s="55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F14" s="99"/>
+      <c r="G14" s="101"/>
+      <c r="H14" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="56">
+        <v>4.8</v>
+      </c>
+      <c r="J14" s="57">
+        <v>1.095</v>
+      </c>
+    </row>
+    <row r="15" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F15" s="99"/>
+      <c r="G15" s="101"/>
+      <c r="H15" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="56">
+        <v>6.6239999999999997</v>
+      </c>
+      <c r="J15" s="57">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="16" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F16" s="99"/>
+      <c r="G16" s="101"/>
+      <c r="H16" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="56">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J16" s="57">
+        <v>1.643</v>
+      </c>
+    </row>
+    <row r="17" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F17" s="99"/>
+      <c r="G17" s="101"/>
+      <c r="H17" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="56">
+        <v>16.8</v>
+      </c>
+      <c r="J17" s="57">
+        <v>2.1680000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F18" s="99"/>
+      <c r="G18" s="101"/>
+      <c r="H18" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" s="56">
+        <v>7</v>
+      </c>
+      <c r="J18" s="57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F19" s="99"/>
+      <c r="G19" s="101"/>
+      <c r="H19" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19" s="56">
+        <v>7</v>
+      </c>
+      <c r="J19" s="57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F20" s="99"/>
+      <c r="G20" s="101"/>
+      <c r="H20" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="56"/>
+      <c r="J20" s="57"/>
+    </row>
+    <row r="21" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F21" s="99"/>
+      <c r="G21" s="101"/>
+      <c r="H21" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="58"/>
+      <c r="J21" s="59"/>
+    </row>
+    <row r="22" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F22" s="99"/>
+      <c r="G22" s="101"/>
+      <c r="H22" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" s="58">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J22" s="59">
+        <v>1.643</v>
+      </c>
+    </row>
+    <row r="23" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F23" s="99"/>
+      <c r="G23" s="102"/>
+      <c r="H23" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="60">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="J23" s="61">
+        <v>2.302</v>
+      </c>
+    </row>
+    <row r="24" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F24" s="99"/>
+      <c r="G24" s="101" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="I24" s="54">
+        <v>0.8</v>
+      </c>
+      <c r="J24" s="55">
+        <v>0.44700000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F25" s="99"/>
+      <c r="G25" s="101"/>
+      <c r="H25" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" s="56">
+        <v>11</v>
+      </c>
+      <c r="J25" s="57">
+        <v>1.871</v>
+      </c>
+    </row>
+    <row r="26" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F26" s="99"/>
+      <c r="G26" s="101"/>
+      <c r="H26" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" s="56">
+        <v>14.638999999999999</v>
+      </c>
+      <c r="J26" s="57">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="27" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F27" s="99"/>
+      <c r="G27" s="101"/>
+      <c r="H27" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="56">
+        <v>22.8</v>
+      </c>
+      <c r="J27" s="57">
+        <v>6.2210000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F28" s="99"/>
+      <c r="G28" s="101"/>
+      <c r="H28" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="56">
+        <v>33.6</v>
+      </c>
+      <c r="J28" s="57">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="29" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F29" s="99"/>
+      <c r="G29" s="101"/>
+      <c r="H29" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" s="56">
+        <v>16</v>
+      </c>
+      <c r="J29" s="57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F30" s="99"/>
+      <c r="G30" s="101"/>
+      <c r="H30" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="I30" s="56">
+        <v>16</v>
+      </c>
+      <c r="J30" s="57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F31" s="99"/>
+      <c r="G31" s="101"/>
+      <c r="H31" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="56"/>
+      <c r="J31" s="57"/>
+    </row>
+    <row r="32" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F32" s="99"/>
+      <c r="G32" s="101"/>
+      <c r="H32" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="I32" s="58"/>
+      <c r="J32" s="59"/>
+    </row>
+    <row r="33" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F33" s="99"/>
+      <c r="G33" s="101"/>
+      <c r="H33" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="I33" s="58">
+        <v>19.8</v>
+      </c>
+      <c r="J33" s="59">
+        <v>5.45</v>
+      </c>
+    </row>
+    <row r="34" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F34" s="99"/>
+      <c r="G34" s="102"/>
+      <c r="H34" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34" s="60">
+        <v>28.2</v>
+      </c>
+      <c r="J34" s="61">
+        <v>3.2709999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F35" s="99"/>
+      <c r="G35" s="101" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="I35" s="54">
+        <v>2.6</v>
+      </c>
+      <c r="J35" s="55">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F36" s="99"/>
+      <c r="G36" s="101"/>
+      <c r="H36" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="I36" s="56">
+        <v>22</v>
+      </c>
+      <c r="J36" s="57">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F37" s="99"/>
+      <c r="G37" s="101"/>
+      <c r="H37" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="I37" s="56">
+        <v>53.951999999999998</v>
+      </c>
+      <c r="J37" s="57">
+        <v>1.4570000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F38" s="99"/>
+      <c r="G38" s="101"/>
+      <c r="H38" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38" s="56">
+        <v>226.8</v>
+      </c>
+      <c r="J38" s="57">
+        <v>47.850999999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F39" s="99"/>
+      <c r="G39" s="101"/>
+      <c r="H39" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="56">
+        <v>361.4</v>
+      </c>
+      <c r="J39" s="57">
+        <v>25.106000000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F40" s="99"/>
+      <c r="G40" s="101"/>
+      <c r="H40" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" s="56">
+        <v>45</v>
+      </c>
+      <c r="J40" s="57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F41" s="99"/>
+      <c r="G41" s="101"/>
+      <c r="H41" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" s="56">
+        <v>45</v>
+      </c>
+      <c r="J41" s="57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F42" s="99"/>
+      <c r="G42" s="101"/>
+      <c r="H42" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="I42" s="56"/>
+      <c r="J42" s="57"/>
+    </row>
+    <row r="43" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F43" s="99"/>
+      <c r="G43" s="101"/>
+      <c r="H43" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="I43" s="58"/>
+      <c r="J43" s="59"/>
+    </row>
+    <row r="44" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F44" s="99"/>
+      <c r="G44" s="101"/>
+      <c r="H44" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" s="58">
+        <v>224.2</v>
+      </c>
+      <c r="J44" s="59">
+        <v>48.884999999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F45" s="99"/>
+      <c r="G45" s="102"/>
+      <c r="H45" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="I45" s="60">
+        <v>371.4</v>
+      </c>
+      <c r="J45" s="61">
+        <v>20.402999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F46" s="99"/>
+      <c r="G46" s="101" t="s">
+        <v>7</v>
+      </c>
+      <c r="H46" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="I46" s="54">
+        <v>2</v>
+      </c>
+      <c r="J46" s="55">
+        <v>1.581</v>
+      </c>
+    </row>
+    <row r="47" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F47" s="99"/>
+      <c r="G47" s="101"/>
+      <c r="H47" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="I47" s="56">
+        <v>16</v>
+      </c>
+      <c r="J47" s="57">
+        <v>2.3450000000000002</v>
+      </c>
+    </row>
+    <row r="48" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F48" s="99"/>
+      <c r="G48" s="101"/>
+      <c r="H48" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="I48" s="56">
+        <v>51.66</v>
+      </c>
+      <c r="J48" s="57">
+        <v>1.4450000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F49" s="99"/>
+      <c r="G49" s="101"/>
+      <c r="H49" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" s="56">
+        <v>179.4</v>
+      </c>
+      <c r="J49" s="57">
+        <v>22.233000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F50" s="99"/>
+      <c r="G50" s="101"/>
+      <c r="H50" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="I50" s="56">
+        <v>239.4</v>
+      </c>
+      <c r="J50" s="57">
+        <v>23.984999999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F51" s="99"/>
+      <c r="G51" s="101"/>
+      <c r="H51" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="I51" s="56">
+        <v>51</v>
+      </c>
+      <c r="J51" s="57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F52" s="99"/>
+      <c r="G52" s="101"/>
+      <c r="H52" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="I52" s="56">
+        <v>51</v>
+      </c>
+      <c r="J52" s="57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F53" s="99"/>
+      <c r="G53" s="101"/>
+      <c r="H53" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="I53" s="56"/>
+      <c r="J53" s="57"/>
+    </row>
+    <row r="54" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F54" s="99"/>
+      <c r="G54" s="101"/>
+      <c r="H54" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="I54" s="58"/>
+      <c r="J54" s="59"/>
+    </row>
+    <row r="55" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F55" s="99"/>
+      <c r="G55" s="101"/>
+      <c r="H55" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="I55" s="58">
+        <v>170.25</v>
+      </c>
+      <c r="J55" s="59">
+        <v>23.768000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F56" s="99"/>
+      <c r="G56" s="102"/>
+      <c r="H56" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="I56" s="60">
+        <v>240.25</v>
+      </c>
+      <c r="J56" s="61">
+        <v>21.407</v>
+      </c>
+    </row>
+    <row r="57" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F57" s="99"/>
+      <c r="G57" s="101" t="s">
+        <v>6</v>
+      </c>
+      <c r="H57" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="I57" s="54">
+        <v>1</v>
+      </c>
+      <c r="J57" s="55">
+        <v>0.70699999999999996</v>
+      </c>
+    </row>
+    <row r="58" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F58" s="99"/>
+      <c r="G58" s="101"/>
+      <c r="H58" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="I58" s="56">
+        <v>15.8</v>
+      </c>
+      <c r="J58" s="57">
+        <v>3.1139999999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F59" s="99"/>
+      <c r="G59" s="101"/>
+      <c r="H59" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="I59" s="56">
+        <v>112.05500000000001</v>
+      </c>
+      <c r="J59" s="57">
+        <v>18.196000000000002</v>
+      </c>
+    </row>
+    <row r="60" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F60" s="99"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="I60" s="56">
+        <v>874.8</v>
+      </c>
+      <c r="J60" s="57">
+        <v>102.072</v>
+      </c>
+    </row>
+    <row r="61" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F61" s="99"/>
+      <c r="G61" s="101"/>
+      <c r="H61" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="I61" s="56">
+        <v>1033.5999999999999</v>
+      </c>
+      <c r="J61" s="57">
+        <v>124.21899999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F62" s="99"/>
+      <c r="G62" s="101"/>
+      <c r="H62" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="I62" s="56">
+        <v>65</v>
+      </c>
+      <c r="J62" s="57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F63" s="99"/>
+      <c r="G63" s="101"/>
+      <c r="H63" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="I63" s="56">
+        <v>65</v>
+      </c>
+      <c r="J63" s="57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F64" s="99"/>
+      <c r="G64" s="101"/>
+      <c r="H64" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="I64" s="56"/>
+      <c r="J64" s="57"/>
+    </row>
+    <row r="65" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F65" s="99"/>
+      <c r="G65" s="101"/>
+      <c r="H65" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="I65" s="58"/>
+      <c r="J65" s="59"/>
+    </row>
+    <row r="66" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F66" s="99"/>
+      <c r="G66" s="101"/>
+      <c r="H66" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="I66" s="58">
+        <v>867.8</v>
+      </c>
+      <c r="J66" s="59">
+        <v>101.57899999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F67" s="99"/>
+      <c r="G67" s="102"/>
+      <c r="H67" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="I67" s="60">
+        <v>1044.5999999999999</v>
+      </c>
+      <c r="J67" s="61">
+        <v>113.931</v>
+      </c>
+    </row>
+    <row r="68" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F68" s="99"/>
+      <c r="G68" s="101" t="s">
+        <v>16</v>
+      </c>
+      <c r="H68" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="I68" s="54">
+        <v>1.8</v>
+      </c>
+      <c r="J68" s="55">
+        <v>1.9239999999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F69" s="99"/>
+      <c r="G69" s="101"/>
+      <c r="H69" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="I69" s="56">
+        <v>21.6</v>
+      </c>
+      <c r="J69" s="57">
+        <v>4.9800000000000004</v>
+      </c>
+    </row>
+    <row r="70" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F70" s="99"/>
+      <c r="G70" s="101"/>
+      <c r="H70" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="I70" s="56">
+        <v>27.3</v>
+      </c>
+      <c r="J70" s="57">
+        <v>1.571</v>
+      </c>
+    </row>
+    <row r="71" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F71" s="99"/>
+      <c r="G71" s="101"/>
+      <c r="H71" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="I71" s="56">
+        <v>34.4</v>
+      </c>
+      <c r="J71" s="57">
+        <v>2.5099999999999998</v>
+      </c>
+    </row>
+    <row r="72" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F72" s="99"/>
+      <c r="G72" s="101"/>
+      <c r="H72" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="I72" s="56">
+        <v>44.4</v>
+      </c>
+      <c r="J72" s="57">
+        <v>2.5099999999999998</v>
+      </c>
+    </row>
+    <row r="73" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F73" s="99"/>
+      <c r="G73" s="101"/>
+      <c r="H73" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="I73" s="56">
+        <v>32</v>
+      </c>
+      <c r="J73" s="57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F74" s="99"/>
+      <c r="G74" s="101"/>
+      <c r="H74" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="I74" s="56">
+        <v>32</v>
+      </c>
+      <c r="J74" s="57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F75" s="99"/>
+      <c r="G75" s="101"/>
+      <c r="H75" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="I75" s="56"/>
+      <c r="J75" s="57"/>
+    </row>
+    <row r="76" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F76" s="99"/>
+      <c r="G76" s="101"/>
+      <c r="H76" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="I76" s="58"/>
+      <c r="J76" s="59"/>
+    </row>
+    <row r="77" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F77" s="99"/>
+      <c r="G77" s="101"/>
+      <c r="H77" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="I77" s="58">
+        <v>29.8</v>
+      </c>
+      <c r="J77" s="59">
+        <v>1.095</v>
+      </c>
+    </row>
+    <row r="78" spans="6:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F78" s="100"/>
+      <c r="G78" s="102"/>
+      <c r="H78" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="I78" s="60">
+        <v>33</v>
+      </c>
+      <c r="J78" s="61">
+        <v>2.7389999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="G8:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="F13:F78"/>
+    <mergeCell ref="G13:G23"/>
+    <mergeCell ref="G24:G34"/>
+    <mergeCell ref="G35:G45"/>
+    <mergeCell ref="G46:G56"/>
+    <mergeCell ref="G57:G67"/>
+    <mergeCell ref="G68:G78"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
